--- a/financial-normalizer/data/样本_序时账.xlsx
+++ b/financial-normalizer/data/样本_序时账.xlsx
@@ -37,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +45,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,390 +417,1438 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:AX11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="26" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
+    <col width="30" customWidth="1" min="22" max="22"/>
+    <col width="30" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
+    <col width="28" customWidth="1" min="25" max="25"/>
+    <col width="28" customWidth="1" min="26" max="26"/>
+    <col width="16" customWidth="1" min="27" max="27"/>
+    <col width="28" customWidth="1" min="28" max="28"/>
+    <col width="28" customWidth="1" min="29" max="29"/>
+    <col width="14" customWidth="1" min="30" max="30"/>
+    <col width="24" customWidth="1" min="31" max="31"/>
+    <col width="24" customWidth="1" min="32" max="32"/>
+    <col width="14" customWidth="1" min="33" max="33"/>
+    <col width="24" customWidth="1" min="34" max="34"/>
+    <col width="24" customWidth="1" min="35" max="35"/>
+    <col width="14" customWidth="1" min="36" max="36"/>
+    <col width="24" customWidth="1" min="37" max="37"/>
+    <col width="24" customWidth="1" min="38" max="38"/>
+    <col width="14" customWidth="1" min="39" max="39"/>
+    <col width="24" customWidth="1" min="40" max="40"/>
+    <col width="24" customWidth="1" min="41" max="41"/>
+    <col width="10" customWidth="1" min="42" max="42"/>
+    <col width="18" customWidth="1" min="43" max="43"/>
+    <col width="18" customWidth="1" min="44" max="44"/>
+    <col width="14" customWidth="1" min="45" max="45"/>
+    <col width="24" customWidth="1" min="46" max="46"/>
+    <col width="24" customWidth="1" min="47" max="47"/>
+    <col width="14" customWidth="1" min="48" max="48"/>
+    <col width="22" customWidth="1" min="49" max="49"/>
+    <col width="22" customWidth="1" min="50" max="50"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>企业主体名称</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>币种</t>
+          <t>凭证日期</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>凭证号</t>
+          <t>字</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>科目编码</t>
+          <t>号</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>科目名称</t>
+          <t>摘要</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>摘要</t>
+          <t>对方科目</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>借方金额</t>
+          <t>本方其他科目</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>贷方金额</t>
+          <t>本位币借方</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>往来单位</t>
+          <t>本位币贷方</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>部门</t>
+          <t>方向</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>项目</t>
+          <t>本位币余额</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>经办人</t>
+          <t>结转分配类型</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>末级科目编号</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>末级科目全路径</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>查询科目</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>查询核算</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>分录行号</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>往来单位编号</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>往来单位名称</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>对方往来单位名称</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>银行账号编号</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>银行账号名称</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>对方银行账号名称</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>采购合同编号</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>采购合同名称</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>对方采购合同名称</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>销售合同编号</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>销售合同名称</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>对方销售合同名称</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>项目编号</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>项目名称</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>对方项目名称</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>资产项目编号</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>资产项目名称</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>对方资产项目名称</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>存货物料编号</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>存货物料名称</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>对方存货物料名称</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>费用项目编号</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>费用项目名称</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>对方费用项目名称</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>部门编号</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>部门名称</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>对方部门名称</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>现金流量编号</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>现金流量名称</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>对方现金流量名称</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>其他编号</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>其他名称</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>对方其他名称</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-01-03</t>
+          <t>样本科技有限公司</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>人民币</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>记-1</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>1001</v>
-      </c>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>库存现金</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>收到股东投资款</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>500000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
+          <t>&gt;期初余额</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>总经办</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
+          <t>借</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>21825.59</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>112201</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>应收账款/客户A</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>应收账款</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>客户A</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-01-05</t>
+          <t>样本科技有限公司</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>人民币</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>记-2</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>1002</v>
+          <t>记账凭证</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>收到客户A货款</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>应收账款/客户A</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>71825.59</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>100201</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>银行存款/工商银行</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>银行存款</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>购买办公设备</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>35000</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>得力办公</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>行政部</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>办公设备采购</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>王五</t>
-        </is>
-      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>工商银行</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0001-001</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>北京客户A有限公司</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0011-1101021119900266558</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>工商银行北京分行人民币活期户</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-01-08</t>
+          <t>样本科技有限公司</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>人民币</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>记-3</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>1122</v>
+          <t>记账凭证</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>确认客户A销售收入</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>银行存款/工商银行</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>21825.59</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>112201</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>应收账款/客户A</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>应收账款</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>销售商品货款未收</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>450000</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>天宇科技</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>销售部</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>A项目尾款</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>赵六</t>
-        </is>
-      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>客户A</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0001-001</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>北京客户A有限公司</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>样本科技有限公司</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>人民币</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>记-4</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>1403</v>
+          <t>付款凭证</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>原材料</t>
+          <t>支付供应商B材料款</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>采购原材料入库</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>120000</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>宝钢集团</t>
-        </is>
+          <t>应付账款/供应商B</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>80000</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>生产部</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>原材料采购</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>钱七</t>
-        </is>
-      </c>
+          <t>贷</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>-80000</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>100201</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>银行存款/工商银行</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>银行存款</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>工商银行</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>0011-1101021119900266558</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>工商银行北京分行人民币活期户</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>PO-2025-0001</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>原材料采购合同2025-001</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>供应商采购合同2025-001</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-01-12</t>
+          <t>样本科技有限公司</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>人民币</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>记-5</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>2001</v>
+          <t>付款凭证</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>短期借款</t>
+          <t>采购原材料入库</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>归还银行借款</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
+          <t>银行存款/工商银行</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>80000</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="n">
-        <v>300000</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>工商银行</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>财务部</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>孙八</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>140301</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>原材料/钢材</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>原材料</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>钢材</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>MAT-001</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Q235B钢材</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>供应商B钢材</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>样本科技有限公司</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>人民币</t>
+          <t>2025-01-25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>记-6</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>6602</v>
+          <t>付款凭证</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>销售部报销差旅费</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>银行存款/工商银行</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>5000</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>贷</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>6601</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>销售费用/差旅费</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>销售费用</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>差旅费</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>EXP-001</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>差旅费</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>D-002</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>销售部</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>样本科技有限公司</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>付款凭证</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>差旅费结转</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>其他应付款/报销户</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>6601</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>销售费用/差旅费</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>销售费用</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>差旅费</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>EXP-001</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>差旅费</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>D-002</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>销售部</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>样本科技有限公司</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>付款凭证</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>研发项目领用材料</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>原材料/钢材</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>贷</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>6602</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>管理费用/研发支出</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>管理费用</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>计提本月工资</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>80000</v>
-      </c>
-      <c r="H7" t="n">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>研发支出</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>P-2025-001</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>新产品研发项目</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>MAT-001</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Q235B钢材</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>样本科技有限公司</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>付款凭证</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>购置生产设备</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>银行存款/工商银行</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>200000</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>贷</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>-200000</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>100201</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>银行存款/工商银行</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>银行存款</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>工商银行</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>0011-1101021119900266558</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>工商银行北京分行人民币活期户</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>样本科技有限公司</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>付款凭证</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>设备验收入库</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>银行存款/工商银行</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>200000</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>人事部</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>周九</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>1601</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>固定资产/机器设备</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>固定资产</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>机器设备</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>FA-2025-001</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>CNC加工中心</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
